--- a/2019.xlsx
+++ b/2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Archana\Desktop\cloudwater\cloudwater data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67886521-F62C-415E-93C9-AF6AC90397C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0B9D7B-1707-49C7-A713-F7C5943ACC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="564" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,7 +116,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +401,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -418,7 +418,7 @@
       <c r="D1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F1" t="s">
@@ -475,7 +475,7 @@
         <v>72.588103970658494</v>
       </c>
       <c r="E2" s="1">
-        <v>43622</v>
+        <v>43622.25</v>
       </c>
       <c r="F2">
         <v>10.8516678027721</v>
@@ -528,7 +528,7 @@
         <v>21.325679051719501</v>
       </c>
       <c r="E3" s="1">
-        <v>43626</v>
+        <v>43626.75</v>
       </c>
       <c r="F3">
         <v>4.0353101567825496</v>
@@ -581,7 +581,7 @@
         <v>17.945038005634402</v>
       </c>
       <c r="E4" s="1">
-        <v>43629</v>
+        <v>43629.75</v>
       </c>
       <c r="F4">
         <v>3.6924517155192</v>
@@ -637,7 +637,7 @@
         <v>8.9725190028172008</v>
       </c>
       <c r="E5" s="1">
-        <v>43631</v>
+        <v>43631.25</v>
       </c>
       <c r="F5">
         <v>1.74271529197909</v>
@@ -687,7 +687,7 @@
         <v>30.468293201509599</v>
       </c>
       <c r="E6" s="1">
-        <v>43633</v>
+        <v>43633.75</v>
       </c>
       <c r="F6">
         <v>5.5397477845944101</v>
@@ -743,7 +743,7 @@
         <v>22.112369106468901</v>
       </c>
       <c r="E7" s="1">
-        <v>43635</v>
+        <v>43635.25</v>
       </c>
       <c r="F7">
         <v>5.1782344921608701</v>
@@ -796,7 +796,7 @@
         <v>5.9320682506777196</v>
       </c>
       <c r="E8" s="1">
-        <v>43636</v>
+        <v>43636.75</v>
       </c>
       <c r="F8">
         <v>1.60390593047034</v>
@@ -849,7 +849,7 @@
         <v>13.841492584914601</v>
       </c>
       <c r="E9" s="1">
-        <v>43637</v>
+        <v>43637.25</v>
       </c>
       <c r="F9">
         <v>2.05219950011361</v>
@@ -899,7 +899,7 @@
         <v>12.416945729017099</v>
       </c>
       <c r="E10" s="1">
-        <v>43641</v>
+        <v>43641.75</v>
       </c>
       <c r="F10">
         <v>2.6716859804589799</v>
@@ -955,7 +955,7 @@
         <v>72.311699356827702</v>
       </c>
       <c r="E11" s="1">
-        <v>43642</v>
+        <v>43642.375</v>
       </c>
       <c r="F11">
         <v>9.4377959554646598</v>
@@ -1008,7 +1008,7 @@
         <v>23.005368628076301</v>
       </c>
       <c r="E12" s="1">
-        <v>43645</v>
+        <v>43645.25</v>
       </c>
       <c r="G12">
         <v>21.6411467941589</v>
@@ -1052,7 +1052,7 @@
         <v>5.3154733429011802</v>
       </c>
       <c r="E13" s="1">
-        <v>43646</v>
+        <v>43646.75</v>
       </c>
       <c r="F13">
         <v>1.76231538286753</v>
@@ -1105,7 +1105,7 @@
         <v>5.61313985010365</v>
       </c>
       <c r="E14" s="1">
-        <v>43647</v>
+        <v>43647.75</v>
       </c>
       <c r="G14">
         <v>2.4355218009267898</v>
@@ -1146,7 +1146,7 @@
         <v>12.6295646627332</v>
       </c>
       <c r="E15" s="1">
-        <v>43648</v>
+        <v>43648.25</v>
       </c>
       <c r="G15">
         <v>13.070395588551399</v>
@@ -1187,7 +1187,7 @@
         <v>30.340721841279901</v>
       </c>
       <c r="E16" s="1">
-        <v>43648</v>
+        <v>43648.75</v>
       </c>
       <c r="G16">
         <v>46.710594070560703</v>
@@ -1231,7 +1231,7 @@
         <v>80.369956944665901</v>
       </c>
       <c r="E17" s="1">
-        <v>43649</v>
+        <v>43649.25</v>
       </c>
       <c r="F17">
         <v>17.668211770052199</v>
@@ -1287,7 +1287,7 @@
         <v>74.395364907244996</v>
       </c>
       <c r="E18" s="1">
-        <v>43652</v>
+        <v>43652.25</v>
       </c>
       <c r="F18">
         <v>10.280313565098799</v>
@@ -1340,7 +1340,7 @@
         <v>65.210226970711702</v>
       </c>
       <c r="E19" s="1">
-        <v>43652</v>
+        <v>43652.75</v>
       </c>
       <c r="F19">
         <v>3.0314133151556399</v>
@@ -1390,7 +1390,7 @@
         <v>1.96140032991171</v>
       </c>
       <c r="E20" s="1">
-        <v>43657</v>
+        <v>43657.75</v>
       </c>
       <c r="F20">
         <v>11.9823085662349</v>
@@ -1443,7 +1443,7 @@
         <v>55.323446552915499</v>
       </c>
       <c r="E21" s="1">
-        <v>43658</v>
+        <v>43658.25</v>
       </c>
       <c r="F21">
         <v>4.2484276300840698</v>
@@ -1496,7 +1496,7 @@
         <v>21.9635358528677</v>
       </c>
       <c r="E22" s="1">
-        <v>43658</v>
+        <v>43658.75</v>
       </c>
       <c r="F22">
         <v>1.8021177005225999</v>
@@ -1549,7 +1549,7 @@
         <v>19.731037048849199</v>
       </c>
       <c r="E23" s="1">
-        <v>43659</v>
+        <v>43659.25</v>
       </c>
       <c r="F23">
         <v>1.7871324698932001</v>
@@ -1602,7 +1602,7 @@
         <v>16.6480625099665</v>
       </c>
       <c r="E24" s="1">
-        <v>43659</v>
+        <v>43659.75</v>
       </c>
       <c r="F24">
         <v>1.9830379459213801</v>
@@ -1658,7 +1658,7 @@
         <v>45.968213469409399</v>
       </c>
       <c r="E25" s="1">
-        <v>43660</v>
+        <v>43660.25</v>
       </c>
       <c r="F25">
         <v>3.1263122017723202</v>
@@ -1714,7 +1714,7 @@
         <v>23.0904162015627</v>
       </c>
       <c r="E26" s="1">
-        <v>43661</v>
+        <v>43661.25</v>
       </c>
       <c r="F26">
         <v>1.33271301976823</v>
@@ -1764,7 +1764,7 @@
         <v>683.83333333333303</v>
       </c>
       <c r="E27" s="1">
-        <v>43661</v>
+        <v>43661.75</v>
       </c>
       <c r="G27">
         <v>13.856047782398701</v>
@@ -1802,7 +1802,7 @@
         <v>0.57188400099144399</v>
       </c>
       <c r="E28" s="1">
-        <v>43662</v>
+        <v>43662.25</v>
       </c>
       <c r="F28">
         <v>2.6406521245171501</v>
@@ -1852,7 +1852,7 @@
         <v>50.284377823845197</v>
       </c>
       <c r="E29" s="1">
-        <v>43663</v>
+        <v>43663.25</v>
       </c>
       <c r="F29">
         <v>2.43591683708248</v>
@@ -1908,7 +1908,7 @@
         <v>36.464147132302102</v>
       </c>
       <c r="E30" s="1">
-        <v>43663</v>
+        <v>43663.75</v>
       </c>
       <c r="F30">
         <v>1.7407566462167601</v>
@@ -1964,7 +1964,7 @@
         <v>30.255674267793498</v>
       </c>
       <c r="E31" s="1">
-        <v>43664</v>
+        <v>43664.25</v>
       </c>
       <c r="F31">
         <v>1.78731879118382</v>
@@ -2017,7 +2017,7 @@
         <v>26.811247541593499</v>
       </c>
       <c r="E32" s="1">
-        <v>43665</v>
+        <v>43665.25</v>
       </c>
       <c r="F32">
         <v>1.6622767552828901</v>
@@ -2073,7 +2073,7 @@
         <v>37.4209323340243</v>
       </c>
       <c r="E33" s="1">
-        <v>43665</v>
+        <v>43665.75</v>
       </c>
       <c r="F33">
         <v>1.9249147920927001</v>
@@ -2129,7 +2129,7 @@
         <v>96.018710466166993</v>
       </c>
       <c r="E34" s="1">
-        <v>43666</v>
+        <v>43666.25</v>
       </c>
       <c r="F34">
         <v>4.2869052488070798</v>
@@ -2179,7 +2179,7 @@
         <v>450.5</v>
       </c>
       <c r="E35" s="1">
-        <v>43666</v>
+        <v>43666.75</v>
       </c>
       <c r="G35">
         <v>111.419765672897</v>
@@ -2220,7 +2220,7 @@
         <v>165.14112581725399</v>
       </c>
       <c r="E36" s="1">
-        <v>43667</v>
+        <v>43667.25</v>
       </c>
       <c r="F36">
         <v>1.0802772097250599</v>
@@ -2276,7 +2276,7 @@
         <v>61.702014564396897</v>
       </c>
       <c r="E37" s="1">
-        <v>43667</v>
+        <v>43667.75</v>
       </c>
       <c r="F37">
         <v>1.50633037945921</v>
@@ -2326,7 +2326,7 @@
         <v>628.33333333333303</v>
       </c>
       <c r="E38" s="1">
-        <v>43668</v>
+        <v>43668.25</v>
       </c>
       <c r="G38">
         <v>52.924388694626202</v>
@@ -2367,7 +2367,7 @@
         <v>16.031467602189899</v>
       </c>
       <c r="E39" s="1">
-        <v>43669</v>
+        <v>43669.25</v>
       </c>
       <c r="F39">
         <v>1.9558395819132</v>
@@ -2420,7 +2420,7 @@
         <v>28.916174985382401</v>
       </c>
       <c r="E40" s="1">
-        <v>43670</v>
+        <v>43670.25</v>
       </c>
       <c r="G40">
         <v>20.855494600311498</v>
@@ -2464,7 +2464,7 @@
         <v>8.0795194812098003</v>
       </c>
       <c r="E41" s="1">
-        <v>43673</v>
+        <v>43673.75</v>
       </c>
       <c r="F41">
         <v>4.1219450124971599</v>
@@ -2517,7 +2517,7 @@
         <v>0.145639780856573</v>
       </c>
       <c r="E42" s="1">
-        <v>43674</v>
+        <v>43674.75</v>
       </c>
       <c r="F42">
         <v>0.97644171779141098</v>
@@ -2570,7 +2570,7 @@
         <v>129.038430872269</v>
       </c>
       <c r="E43" s="1">
-        <v>43675</v>
+        <v>43675.25</v>
       </c>
       <c r="F43">
         <v>9.1230015905476005</v>
@@ -2626,7 +2626,7 @@
         <v>84.707383192473202</v>
       </c>
       <c r="E44" s="1">
-        <v>43675</v>
+        <v>43675.75</v>
       </c>
       <c r="F44">
         <v>4.8441240627130204</v>
@@ -2682,7 +2682,7 @@
         <v>174.94285866156301</v>
       </c>
       <c r="E45" s="1">
-        <v>43676</v>
+        <v>43676.75</v>
       </c>
       <c r="F45">
         <v>15.0796796182685</v>
@@ -2738,7 +2738,7 @@
         <v>54.2603518843353</v>
       </c>
       <c r="E46" s="1">
-        <v>43677</v>
+        <v>43677.75</v>
       </c>
       <c r="F46">
         <v>1.4151033855941799</v>
@@ -2785,7 +2785,7 @@
         <v>1921604</v>
       </c>
       <c r="E47" s="1">
-        <v>43681</v>
+        <v>43681.25</v>
       </c>
       <c r="G47">
         <v>-0.16855810704361299</v>
@@ -2823,7 +2823,7 @@
         <v>0.17540875719010901</v>
       </c>
       <c r="E48" s="1">
-        <v>43683</v>
+        <v>43683.25</v>
       </c>
       <c r="F48">
         <v>1.6965167007498301</v>
@@ -2876,7 +2876,7 @@
         <v>57.555945356933996</v>
       </c>
       <c r="E49" s="1">
-        <v>43684</v>
+        <v>43684.75</v>
       </c>
       <c r="F49">
         <v>3.08370597591456</v>
@@ -2932,7 +2932,7 @@
         <v>46.818689204273603</v>
       </c>
       <c r="E50" s="1">
-        <v>43685</v>
+        <v>43685.25</v>
       </c>
       <c r="F50">
         <v>1.8399659168370801</v>
@@ -2988,7 +2988,7 @@
         <v>25.2591293254664</v>
       </c>
       <c r="E51" s="1">
-        <v>43685</v>
+        <v>43685.75</v>
       </c>
       <c r="F51">
         <v>1.2905407861849501</v>
@@ -3044,7 +3044,7 @@
         <v>28.490937117950299</v>
       </c>
       <c r="E52" s="1">
-        <v>43686</v>
+        <v>43686.25</v>
       </c>
       <c r="F52">
         <v>1.0091729152465301</v>
@@ -3100,7 +3100,7 @@
         <v>14.628182639664001</v>
       </c>
       <c r="E53" s="1">
-        <v>43686</v>
+        <v>43686.75</v>
       </c>
       <c r="F53">
         <v>1.15184957964099</v>
@@ -3156,7 +3156,7 @@
         <v>16.924467123797299</v>
       </c>
       <c r="E54" s="1">
-        <v>43687</v>
+        <v>43687.25</v>
       </c>
       <c r="F54">
         <v>1.25935241990456</v>
@@ -3209,7 +3209,7 @@
         <v>9.1213522564184295</v>
       </c>
       <c r="E55" s="1">
-        <v>43687</v>
+        <v>43687.75</v>
       </c>
       <c r="F55">
         <v>0.87743012951601895</v>
@@ -3265,7 +3265,7 @@
         <v>11.481422420666499</v>
       </c>
       <c r="E56" s="1">
-        <v>43688</v>
+        <v>43688.25</v>
       </c>
       <c r="F56">
         <v>0.98869802317654998</v>
@@ -3315,7 +3315,7 @@
         <v>282.666666666666</v>
       </c>
       <c r="E57" s="1">
-        <v>43688</v>
+        <v>43688.75</v>
       </c>
       <c r="F57">
         <v>0.89758463985457804</v>
@@ -3365,7 +3365,7 @@
         <v>37.484718014139098</v>
       </c>
       <c r="E58" s="1">
-        <v>43689</v>
+        <v>43689.25</v>
       </c>
       <c r="F58">
         <v>1.1369325153374199</v>
@@ -3421,7 +3421,7 @@
         <v>64.040822835273403</v>
       </c>
       <c r="E59" s="1">
-        <v>43690</v>
+        <v>43690.25</v>
       </c>
       <c r="F59">
         <v>3.40801181549647</v>
@@ -3474,7 +3474,7 @@
         <v>25.344176898952799</v>
       </c>
       <c r="E60" s="1">
-        <v>43693</v>
+        <v>43693.25</v>
       </c>
       <c r="G60">
         <v>28.069210198364502</v>
@@ -3518,7 +3518,7 @@
         <v>61.893371604741397</v>
       </c>
       <c r="E61" s="1">
-        <v>43693</v>
+        <v>43693.75</v>
       </c>
       <c r="F61">
         <v>3.4559827311974498</v>
@@ -3574,7 +3574,7 @@
         <v>148.04656354648299</v>
       </c>
       <c r="E62" s="1">
-        <v>43694</v>
+        <v>43694.25</v>
       </c>
       <c r="F62">
         <v>4.3072642581231504</v>
@@ -3627,7 +3627,7 @@
         <v>123.999362143198</v>
       </c>
       <c r="E63" s="1">
-        <v>43694</v>
+        <v>43694.75</v>
       </c>
       <c r="G63">
         <v>118.56205834423599</v>
@@ -3671,7 +3671,7 @@
         <v>57.640992930420403</v>
       </c>
       <c r="E64" s="1">
-        <v>43695</v>
+        <v>43695.25</v>
       </c>
       <c r="F64">
         <v>1.23257668711656</v>
@@ -3724,7 +3724,7 @@
         <v>58.576516238770999</v>
       </c>
       <c r="E65" s="1">
-        <v>43695</v>
+        <v>43695.75</v>
       </c>
       <c r="F65">
         <v>1.1806543967280101</v>
@@ -3777,7 +3777,7 @@
         <v>59.490777653750001</v>
       </c>
       <c r="E66" s="1">
-        <v>43696</v>
+        <v>43696.25</v>
       </c>
       <c r="F66">
         <v>1.3379459213814999</v>
@@ -3830,7 +3830,7 @@
         <v>45.713070748950102</v>
       </c>
       <c r="E67" s="1">
-        <v>43698</v>
+        <v>43698.75</v>
       </c>
       <c r="F67">
         <v>4.7888957055214698</v>
@@ -3886,7 +3886,7 @@
         <v>29.617817466645398</v>
       </c>
       <c r="E68" s="1">
-        <v>43699</v>
+        <v>43699.25</v>
       </c>
       <c r="F68">
         <v>1.6949920472619799</v>
@@ -3939,7 +3939,7 @@
         <v>35.4435762504651</v>
       </c>
       <c r="E69" s="1">
-        <v>43699</v>
+        <v>43699.75</v>
       </c>
       <c r="F69">
         <v>2.2942149511474601</v>
@@ -3995,7 +3995,7 @@
         <v>11.991707861585001</v>
       </c>
       <c r="E70" s="1">
-        <v>43700</v>
+        <v>43700.25</v>
       </c>
       <c r="F70">
         <v>2.8859463758236701</v>
@@ -4048,7 +4048,7 @@
         <v>-119.364269388189</v>
       </c>
       <c r="E71" s="1">
-        <v>43700</v>
+        <v>43700.75</v>
       </c>
       <c r="F71">
         <v>1.4428675301067899</v>
@@ -4089,7 +4089,7 @@
         <v>-176.72885770477799</v>
       </c>
       <c r="E72" s="1">
-        <v>43701</v>
+        <v>43701.25</v>
       </c>
       <c r="F72">
         <v>1.69373097023403</v>
@@ -4130,7 +4130,7 @@
         <v>22.856535374475101</v>
       </c>
       <c r="E73" s="1">
-        <v>43701</v>
+        <v>43701.75</v>
       </c>
       <c r="F73">
         <v>0.80324926153147003</v>
@@ -4186,7 +4186,7 @@
         <v>18.880561313985002</v>
       </c>
       <c r="E74" s="1">
-        <v>43702</v>
+        <v>43702.25</v>
       </c>
       <c r="F74">
         <v>2.7237968643490098</v>
@@ -4242,7 +4242,7 @@
         <v>26.556104821134301</v>
       </c>
       <c r="E75" s="1">
-        <v>43705</v>
+        <v>43705.25</v>
       </c>
       <c r="F75">
         <v>2.0531947284708001</v>
@@ -4298,7 +4298,7 @@
         <v>36.549194705788501</v>
       </c>
       <c r="E76" s="1">
-        <v>43707</v>
+        <v>43707.25</v>
       </c>
       <c r="F76">
         <v>1.5026971142922001</v>
@@ -4354,7 +4354,7 @@
         <v>21.5595598788072</v>
       </c>
       <c r="E77" s="1">
-        <v>43707</v>
+        <v>43707.75</v>
       </c>
       <c r="F77">
         <v>1.6293387866394</v>
@@ -4407,7 +4407,7 @@
         <v>7.1439961728591896</v>
       </c>
       <c r="E78" s="1">
-        <v>43708</v>
+        <v>43708.25</v>
       </c>
       <c r="G78">
         <v>15.713043876946999</v>
@@ -4451,7 +4451,7 @@
         <v>8.9512571094455904</v>
       </c>
       <c r="E79" s="1">
-        <v>43708</v>
+        <v>43708.75</v>
       </c>
       <c r="F79">
         <v>1.686775732788</v>
@@ -4504,7 +4504,7 @@
         <v>7.1865199596023999</v>
       </c>
       <c r="E80" s="1">
-        <v>43709</v>
+        <v>43709.25</v>
       </c>
       <c r="G80">
         <v>4.2639487247897199</v>
@@ -4545,7 +4545,7 @@
         <v>4.69887843512464</v>
       </c>
       <c r="E81" s="1">
-        <v>43710</v>
+        <v>43710.25</v>
       </c>
       <c r="G81">
         <v>9.4992492528816204</v>
@@ -4589,7 +4589,7 @@
         <v>11.7365651411258</v>
       </c>
       <c r="E82" s="1">
-        <v>43710</v>
+        <v>43710.75</v>
       </c>
       <c r="F82">
         <v>1.0018109520563501</v>
@@ -4645,7 +4645,7 @@
         <v>12.5019933025035</v>
       </c>
       <c r="E83" s="1">
-        <v>43711</v>
+        <v>43711.25</v>
       </c>
       <c r="F83">
         <v>1.52517155192001</v>
@@ -4701,7 +4701,7 @@
         <v>12.0342316483282</v>
       </c>
       <c r="E84" s="1">
-        <v>43711</v>
+        <v>43711.75</v>
       </c>
       <c r="F84">
         <v>0.86873210633946796</v>
@@ -4751,7 +4751,7 @@
         <v>50.390687290703198</v>
       </c>
       <c r="E85" s="1">
-        <v>43712</v>
+        <v>43712.25</v>
       </c>
       <c r="F85">
         <v>1.9202567598273099</v>
@@ -4804,7 +4804,7 @@
         <v>28.278318184234301</v>
       </c>
       <c r="E86" s="1">
-        <v>43712</v>
+        <v>43712.75</v>
       </c>
       <c r="F86">
         <v>0.95716655305612297</v>
@@ -4857,7 +4857,7 @@
         <v>6.1021633976505596</v>
       </c>
       <c r="E87" s="1">
-        <v>43713</v>
+        <v>43713.25</v>
       </c>
       <c r="F87">
         <v>1.0200431720063601</v>
@@ -4910,7 +4910,7 @@
         <v>3.7846170201456402</v>
       </c>
       <c r="E88" s="1">
-        <v>43714</v>
+        <v>43714.25</v>
       </c>
       <c r="G88">
         <v>0.57352610150856698</v>
@@ -4963,7 +4963,7 @@
         <v>14.925849146866501</v>
       </c>
       <c r="E89" s="1">
-        <v>43715</v>
+        <v>43715.75</v>
       </c>
       <c r="F89">
         <v>1.1400227221086101</v>
@@ -5019,7 +5019,7 @@
         <v>8.8449476425875702</v>
       </c>
       <c r="E90" s="1">
-        <v>43716</v>
+        <v>43716.25</v>
       </c>
       <c r="F90">
         <v>0.84974551238354901</v>
@@ -5072,7 +5072,7 @@
         <v>13.054802530165301</v>
       </c>
       <c r="E91" s="1">
-        <v>43716</v>
+        <v>43716.75</v>
       </c>
       <c r="F91">
         <v>0.82130652124517101</v>
@@ -5125,7 +5125,7 @@
         <v>10.822303726146799</v>
       </c>
       <c r="E92" s="1">
-        <v>43717</v>
+        <v>43717.25</v>
       </c>
       <c r="F92">
         <v>0.93134287661894999</v>
@@ -5181,7 +5181,7 @@
         <v>28.916174985382401</v>
       </c>
       <c r="E93" s="1">
-        <v>43718</v>
+        <v>43718.25</v>
       </c>
       <c r="F93">
         <v>1.1707657350602101</v>
@@ -5237,7 +5237,7 @@
         <v>62.509966512517899</v>
       </c>
       <c r="E94" s="1">
-        <v>43719</v>
+        <v>43719.25</v>
       </c>
       <c r="F94">
         <v>1.69521472392638</v>
@@ -5293,7 +5293,7 @@
         <v>49.965449423271103</v>
       </c>
       <c r="E95" s="1">
-        <v>43719</v>
+        <v>43719.75</v>
       </c>
       <c r="F95">
         <v>1.1534355828220799</v>
@@ -5349,7 +5349,7 @@
         <v>22.537606973900999</v>
       </c>
       <c r="E96" s="1">
-        <v>43720</v>
+        <v>43720.25</v>
       </c>
       <c r="F96">
         <v>1.3118950238582101</v>
@@ -5402,7 +5402,7 @@
         <v>27.002604581938002</v>
       </c>
       <c r="E97" s="1">
-        <v>43720</v>
+        <v>43720.75</v>
       </c>
       <c r="F97">
         <v>0.78208588957055203</v>
@@ -5458,7 +5458,7 @@
         <v>68.888534523999297</v>
       </c>
       <c r="E98" s="1">
-        <v>43722</v>
+        <v>43722.25</v>
       </c>
       <c r="F98">
         <v>1.8272029084299</v>
@@ -5511,7 +5511,7 @@
         <v>34.444267261999599</v>
       </c>
       <c r="E99" s="1">
-        <v>43722</v>
+        <v>43722.75</v>
       </c>
       <c r="F99">
         <v>0.93229493296977906</v>
@@ -5564,7 +5564,7 @@
         <v>62.7225854462339</v>
       </c>
       <c r="E100" s="1">
-        <v>43723</v>
+        <v>43723.25</v>
       </c>
       <c r="F100">
         <v>1.42334923880936</v>
@@ -5620,7 +5620,7 @@
         <v>37.4209323340243</v>
       </c>
       <c r="E101" s="1">
-        <v>43723</v>
+        <v>43723.75</v>
       </c>
       <c r="F101">
         <v>0.86893206089525099</v>
@@ -5676,7 +5676,7 @@
         <v>21.240631478233102</v>
       </c>
       <c r="E102" s="1">
-        <v>43724</v>
+        <v>43724.25</v>
       </c>
       <c r="F102">
         <v>1.0356714383094701</v>
@@ -5729,7 +5729,7 @@
         <v>14.2454685589751</v>
       </c>
       <c r="E103" s="1">
-        <v>43730</v>
+        <v>43730.25</v>
       </c>
       <c r="G103">
         <v>1.1999051687850399</v>
@@ -5770,7 +5770,7 @@
         <v>6.8038058789135096</v>
       </c>
       <c r="E104" s="1">
-        <v>43730</v>
+        <v>43730.75</v>
       </c>
       <c r="F104">
         <v>0.76605544194501196</v>
@@ -5826,7 +5826,7 @@
         <v>166.90586296709699</v>
       </c>
       <c r="E105" s="1">
-        <v>43731</v>
+        <v>43731.25</v>
       </c>
       <c r="F105">
         <v>2.3477414224039901</v>
@@ -5882,7 +5882,7 @@
         <v>64.848774783394404</v>
       </c>
       <c r="E106" s="1">
-        <v>43731</v>
+        <v>43731.75</v>
       </c>
       <c r="F106">
         <v>2.00261077027948</v>
@@ -5935,7 +5935,7 @@
         <v>13.1185882102801</v>
       </c>
       <c r="E107" s="1">
-        <v>43732</v>
+        <v>43732.25</v>
       </c>
       <c r="F107">
         <v>0.81712565326062203</v>
@@ -5988,7 +5988,7 @@
         <v>8.2921384149258497</v>
       </c>
       <c r="E108" s="1">
-        <v>43732</v>
+        <v>43732.75</v>
       </c>
       <c r="F108">
         <v>1.02967280163599</v>
@@ -6041,7 +6041,7 @@
         <v>7.9306862276085601</v>
       </c>
       <c r="E109" s="1">
-        <v>43733</v>
+        <v>43733.25</v>
       </c>
       <c r="F109">
         <v>0.962678936605317</v>
@@ -6097,7 +6097,7 @@
         <v>16.052729495561501</v>
       </c>
       <c r="E110" s="1">
-        <v>43733</v>
+        <v>43733.75</v>
       </c>
       <c r="F110">
         <v>1.16605544194501</v>
@@ -6141,7 +6141,7 @@
         <v>105.458991123159</v>
       </c>
       <c r="E111" s="1">
-        <v>43734</v>
+        <v>43734.25</v>
       </c>
       <c r="F111">
         <v>1.7253215178368499</v>
@@ -6182,7 +6182,7 @@
         <v>38.909264870036601</v>
       </c>
       <c r="E112" s="1">
-        <v>43734</v>
+        <v>43734.75</v>
       </c>
       <c r="F112">
         <v>0.84118836628038995</v>
@@ -6223,7 +6223,7 @@
         <v>17.796204752033098</v>
       </c>
       <c r="E113" s="1">
-        <v>43735</v>
+        <v>43735.25</v>
       </c>
       <c r="F113">
         <v>0.84641217905021504</v>
@@ -6264,7 +6264,7 @@
         <v>17.456014458087399</v>
       </c>
       <c r="E114" s="1">
-        <v>43735</v>
+        <v>43735.75</v>
       </c>
       <c r="G114">
         <v>8.4993282788940796</v>
@@ -6293,7 +6293,7 @@
         <v>48.902354754690897</v>
       </c>
       <c r="E115" s="1">
-        <v>43736</v>
+        <v>43736.75</v>
       </c>
       <c r="G115">
         <v>40.2825306663551</v>
@@ -6322,7 +6322,7 @@
         <v>7.8456386541221397</v>
       </c>
       <c r="E116" s="1">
-        <v>43737</v>
+        <v>43737.25</v>
       </c>
       <c r="G116">
         <v>3.1140396047040499</v>
@@ -6351,7 +6351,7 @@
         <v>23.3880827087652</v>
       </c>
       <c r="E117" s="1">
-        <v>43737</v>
+        <v>43737.75</v>
       </c>
       <c r="G117">
         <v>4.6067787730140202</v>
@@ -6380,7 +6380,7 @@
         <v>12.3318981555307</v>
       </c>
       <c r="E118" s="1">
-        <v>43739</v>
+        <v>43739.25</v>
       </c>
       <c r="G118">
         <v>10.6420160802959</v>
